--- a/AAII_Financials/Quarterly/SGSOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SGSOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
   <si>
     <t>SGSOY</t>
   </si>
@@ -656,83 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,8 +786,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +839,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +892,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +917,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +966,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1019,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1072,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1125,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,8 +1147,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1142,8 +1196,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,8 +1249,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,8 +1274,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1255,8 +1323,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,8 +1376,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,8 +1429,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1396,8 +1482,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1443,8 +1535,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,8 +1588,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1537,8 +1641,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1584,8 +1694,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1747,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1800,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,8 +1906,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1819,8 +1959,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1866,8 +2012,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,8 +2065,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1960,60 +2118,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,70 +2222,78 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1608900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1620700</v>
+      </c>
+      <c r="F41" s="3">
         <v>2938400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2922100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2128800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1915300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1335300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1432400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1433300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1427900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1863300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1715700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1176700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1153800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1755200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1653700</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1300</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2144,337 +2324,385 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2297000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2313900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1939600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1928800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2068500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1861000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1722600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1848000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1878500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1871300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1764700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1624900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1862900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1826600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1666500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1570100</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>76000</v>
+      </c>
+      <c r="F44" s="3">
         <v>69400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>69000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>67900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>61100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>60700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>65100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>62300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>62100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>67700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>62300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>71500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>70100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>63800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>60100</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F45" s="3">
         <v>13900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>13800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>22100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>23700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>20200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>18600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>13000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3988900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4018100</v>
+      </c>
+      <c r="F46" s="3">
         <v>4962500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4934900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4265200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3837300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3140700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3369200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3374100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3361200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3715900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3421600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3111100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3050600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3498500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3296200</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7600</v>
+        <v>7400</v>
       </c>
       <c r="E47" s="3">
         <v>7500</v>
       </c>
       <c r="F47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="G47" s="3">
+        <v>7500</v>
+      </c>
+      <c r="H47" s="3">
         <v>23900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>21500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>21000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>22500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>20000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>20000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>19000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>17500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>24600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>24100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>21600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1783400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1796500</v>
+      </c>
+      <c r="F48" s="3">
         <v>1683600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1674200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1618300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1456000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1528400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1639600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1583600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1577500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1578300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1453300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1584600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1553800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1604900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1512100</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4255000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4286100</v>
+      </c>
+      <c r="F49" s="3">
         <v>2790800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2775300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2646900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2381400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2303100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2470700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2209000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2200500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2269400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2089700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2330000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2284600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2276500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2144800</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,55 +2801,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>220300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>221900</v>
+      </c>
+      <c r="F52" s="3">
         <v>247200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>245800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>213800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>192300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>214100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>229700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>247100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>246100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>222100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>204500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>148600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>145700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>130900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>123300</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2907,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10480200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10557000</v>
+      </c>
+      <c r="F54" s="3">
         <v>9941400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9886100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9032000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8126000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7447700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7989700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>7675300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7645900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8029100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>7393200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>7384400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>7240700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>7702200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7256700</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,290 +3006,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>899800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>906300</v>
+      </c>
+      <c r="F57" s="3">
         <v>382100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>380000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>792200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>712700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>342100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>367000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>742300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>739400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>397800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>366300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>748700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>734200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>389300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>366800</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1887400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1901200</v>
+      </c>
+      <c r="F58" s="3">
         <v>1247200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1240300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1648500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1483100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>850800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>912700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>913600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>910100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1168600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1076000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1563400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1532900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1266400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1193100</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1403500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1413800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1397300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1389600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1325300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1192400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1230400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1320000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1095000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1090800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1496300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1377800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1058300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1037700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1439400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1356200</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4190600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4221300</v>
+      </c>
+      <c r="F60" s="3">
         <v>3441600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3422500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3766000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3388200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2786400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2989200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2750900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2740400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3062700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2820200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3370400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3304800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3095200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2916100</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4568100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4601600</v>
+      </c>
+      <c r="F61" s="3">
         <v>4928400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4901100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4055200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3648400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3430900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3680600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3882700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3867900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4066200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3744200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3346900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3281800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3541800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3336900</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>187000</v>
+      </c>
+      <c r="F62" s="3">
         <v>145000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>144200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>118200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>106300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>111500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>119600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>113500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>113100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>108100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>99500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>107300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>105200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>103800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>97800</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3479,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9090300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9157000</v>
+      </c>
+      <c r="F66" s="3">
         <v>8686600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8638300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8097800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7285500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6479900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6951500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6908500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6882100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>7402100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6815800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6962000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>6826500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6877000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6479300</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3712,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3765,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3707900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3735100</v>
+      </c>
+      <c r="F72" s="3">
         <v>3682500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3662000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3281900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2952700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2830600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3036500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2801000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2790300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2895300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2666000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2426100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2378900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2703700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2547300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3977,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1246300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1255400</v>
+      </c>
+      <c r="F76" s="3">
         <v>1136300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1130000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>806000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>725200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>879500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>943500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>665500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>662900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>545100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>501900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>319600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>313400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>737600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>694900</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,60 +4083,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3804,8 +4194,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,55 +4219,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>136900</v>
+      </c>
+      <c r="F83" s="3">
         <v>95500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>102400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>133500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>133000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>113400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>104400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>127400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>124900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>108700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>102400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>123600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>128100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>111300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>108800</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4533,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>300500</v>
+      </c>
+      <c r="F89" s="3">
         <v>505100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>502300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>265300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>238700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>456300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>489500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>220900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>220100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>447700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>412300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>206200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>202200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>414700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>390800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4611,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-81700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-85100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-84700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-68500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-61700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-51900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-55600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-75700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-75400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-92000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-84700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-79900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-78300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-93500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-88100</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4766,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-811300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-817200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-119800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-119100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-75400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-67900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-138500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-148600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-79000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-78700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-61200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-56300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-77700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-76200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-116800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-110000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,55 +4844,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>147900</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>139600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>125600</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>115200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>114700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>329700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>323200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,145 +5052,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-130600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-131500</v>
+      </c>
+      <c r="F100" s="3">
         <v>31500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>31400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>150300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>135200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-354800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-380600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-306600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-305400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-46300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-42600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-425200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-416900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-6100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-6500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>8300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>8300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-33800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-31200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-21800</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-21400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-22700</v>
       </c>
       <c r="M101" s="3">
         <v>-21400</v>
       </c>
       <c r="N101" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="P101" s="3">
         <v>-14700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-15200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-23600</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-637400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-642000</v>
+      </c>
+      <c r="F102" s="3">
         <v>401700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>399400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>303700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>273200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-43000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-46200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-156400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-155800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>306400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>282100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-318500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-312300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>273100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>257300</v>
       </c>
     </row>
